--- a/results/Int Task Remove ACC 0.4/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC 0.4/Rando_4_permute.xlsx
@@ -440,747 +440,747 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6015457415631892</v>
+        <v>0.5906994924317955</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5988719447717453</v>
+        <v>0.5889339557086317</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6068045862412762</v>
+        <v>0.5859070515725551</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6087211849300583</v>
+        <v>0.6075240188525333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6096672104897429</v>
+        <v>0.6092895555756972</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6378176077827125</v>
+        <v>0.6194295900178253</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.653847170609384</v>
+        <v>0.608215127345237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6575802894347261</v>
+        <v>0.622365856974531</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6645291398531677</v>
+        <v>0.6183551617873652</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6548932747212907</v>
+        <v>0.6187082691319979</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6715289736850056</v>
+        <v>0.6219749841384936</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6701920752892836</v>
+        <v>0.670607495694734</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6554484274449379</v>
+        <v>0.6618440134143025</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6460278256140668</v>
+        <v>0.6753262938457355</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6213952838454334</v>
+        <v>0.6571894165986888</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6213952838454334</v>
+        <v>0.6698899513580471</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6169937158222303</v>
+        <v>0.6620328408713254</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6123901024200127</v>
+        <v>0.6620328408713254</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6130963171092783</v>
+        <v>0.6858704190458926</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6140423426689627</v>
+        <v>0.7039695308015348</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6300095924348168</v>
+        <v>0.7031877851294601</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6353194205262999</v>
+        <v>0.6888595576905646</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6375513610683102</v>
+        <v>0.6569496057282698</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6372737847064865</v>
+        <v>0.6577068038309315</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6549310402126952</v>
+        <v>0.6497987099308136</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6624595909241972</v>
+        <v>0.6521571648690293</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6624595909241972</v>
+        <v>0.6511733738179402</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6729149672195535</v>
+        <v>0.6521193993776246</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6729149672195535</v>
+        <v>0.6273735611347775</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6922244629747122</v>
+        <v>0.6260876461524518</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7094908456448835</v>
+        <v>0.6395944741532977</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7293177286322849</v>
+        <v>0.6632545545182633</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.750354995619203</v>
+        <v>0.6658905858183026</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7542523943321551</v>
+        <v>0.6654751654128523</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7503814314631863</v>
+        <v>0.6771031602163207</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7496752167739207</v>
+        <v>0.6609206471494607</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7554892141756548</v>
+        <v>0.6689552554457838</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.721978005377806</v>
+        <v>0.6689552554457838</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7100592162905224</v>
+        <v>0.6504407232846914</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6953042387987552</v>
+        <v>0.6310934620381281</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6998323212181636</v>
+        <v>0.6279778089972508</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6857212453548446</v>
+        <v>0.6446890389437747</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6857212453548446</v>
+        <v>0.6373738632587087</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6990770113900722</v>
+        <v>0.6373738632587087</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7234055409528989</v>
+        <v>0.6367054140608478</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7300900329315085</v>
+        <v>0.6367054140608478</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7294215837336475</v>
+        <v>0.6320640351672255</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.728739916613795</v>
+        <v>0.6336785099247711</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7277447959152845</v>
+        <v>0.6324039245898667</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7243780023565667</v>
+        <v>0.6031054563581981</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7143777002326355</v>
+        <v>0.6567834375660896</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6829511465603191</v>
+        <v>0.6604787909000271</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6358311429348318</v>
+        <v>0.6545382791020876</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6513810840206653</v>
+        <v>0.6529747877579383</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6554824163872021</v>
+        <v>0.6529747877579383</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6280892171968941</v>
+        <v>0.6533278951025711</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6206626333121846</v>
+        <v>0.6536432369557993</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6155038671863198</v>
+        <v>0.6440583552373184</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.653913260219342</v>
+        <v>0.6285121907006254</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.653913260219342</v>
+        <v>0.6210232937550983</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.649827034049367</v>
+        <v>0.6258402821837518</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6591721048974289</v>
+        <v>0.6193068521707604</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6591343394060244</v>
+        <v>0.5811655941267108</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6185893078340735</v>
+        <v>0.5542784525212242</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5955051512130276</v>
+        <v>0.5510249554367201</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6034245747605668</v>
+        <v>0.557356340070697</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6034245747605668</v>
+        <v>0.5818378198737122</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6035133236653676</v>
+        <v>0.5886488262485271</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5946554276564247</v>
+        <v>0.5777893591951418</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5674925979636847</v>
+        <v>0.5917890268588175</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5710029003897399</v>
+        <v>0.4927792380434454</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.540390193057192</v>
+        <v>0.4927792380434454</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5596430405752439</v>
+        <v>0.4924638961902172</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6067800386718631</v>
+        <v>0.4967521677392066</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5851139762530591</v>
+        <v>0.5547316384180792</v>
       </c>
     </row>
     <row r="77">
@@ -1190,137 +1190,137 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.561740913622768</v>
+        <v>0.5698529411764706</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5395914529139854</v>
+        <v>0.5680118734704976</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5787467144022478</v>
+        <v>0.5791753527296897</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5645733254781111</v>
+        <v>0.5791753527296897</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5541594912232998</v>
+        <v>0.5896193993776246</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.553542025438835</v>
+        <v>0.5863564609202695</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.553542025438835</v>
+        <v>0.5867095682649023</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5829292425753043</v>
+        <v>0.601188857669416</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5835976917731653</v>
+        <v>0.6020253633040273</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5375709991238407</v>
+        <v>0.57892987703556</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.542363439983081</v>
+        <v>0.570821626030998</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4920730233541799</v>
+        <v>0.5466403818846491</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4920730233541799</v>
+        <v>0.4995354844557237</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4883096921357141</v>
+        <v>0.4995354844557237</v>
       </c>
     </row>
   </sheetData>
